--- a/formshare/tests/resources/forms/bad_language/bad_language.xlsx
+++ b/formshare/tests/resources/forms/bad_language/bad_language.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" state="visible" r:id="rId2"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
   <si>
     <t xml:space="preserve">type</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t xml:space="preserve">form_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">version</t>
   </si>
   <si>
     <t xml:space="preserve">Solo una prueba</t>
@@ -330,7 +333,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="13.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.69"/>
@@ -449,7 +452,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="13.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="13.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.64"/>
@@ -542,8 +545,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="9.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.41"/>
@@ -557,13 +560,19 @@
       <c r="B1" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="C1" s="0" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
